--- a/assets/2026臺北數位藝術節_活動清冊.xlsx
+++ b/assets/2026臺北數位藝術節_活動清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2758732-92D1-491C-9121-6BB6F5B39735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E046ADC4-8562-4F82-BAA3-496FA1EA6C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="585" windowWidth="28740" windowHeight="19065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作坊&amp;講座" sheetId="7" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
   <si>
     <t>簡介中文</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1198,6 +1198,62 @@
         <scheme val="minor"/>
       </rPr>
       <t>15:00-15:30</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報名機制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>人，預先報名</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>人，預先報名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>現場候補</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1576,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1586,13 +1642,13 @@
     <col min="5" max="5" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" style="2" customWidth="1"/>
-    <col min="8" max="9" width="21.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="10" width="21.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="45.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -1621,11 +1677,14 @@
         <v>1</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1654,10 +1713,13 @@
         <v>78</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1686,10 +1748,13 @@
         <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>50</v>
       </c>
@@ -1712,10 +1777,13 @@
         <v>14</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>50</v>
       </c>
@@ -1738,10 +1806,13 @@
         <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>50</v>
       </c>
@@ -1764,10 +1835,13 @@
         <v>14</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>50</v>
       </c>
@@ -1790,10 +1864,13 @@
         <v>14</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>50</v>
       </c>
@@ -1816,10 +1893,13 @@
         <v>14</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>50</v>
       </c>
@@ -1842,38 +1922,41 @@
         <v>14</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="D10" s="4"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="D11" s="4"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="3"/>
       <c r="D16" s="3"/>

--- a/assets/2026臺北數位藝術節_活動清冊.xlsx
+++ b/assets/2026臺北數位藝術節_活動清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E046ADC4-8562-4F82-BAA3-496FA1EA6C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4320F78F-DE5F-4665-92C6-B33F3C82A4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作坊&amp;講座" sheetId="7" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="80">
   <si>
     <t>簡介中文</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -882,53 +882,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Artist Talk 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藝術家講座一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藝術家講座二</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Artist Talk 2</t>
-  </si>
-  <si>
-    <t>Artist Talk 3</t>
-  </si>
-  <si>
-    <t>Artist Talk 4</t>
-  </si>
-  <si>
-    <t>Artist Talk 5</t>
-  </si>
-  <si>
-    <t>Artist Talk 6</t>
-  </si>
-  <si>
     <t>講座</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>藝術家講座三</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藝術家講座四</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藝術家講座五</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藝術家講座六</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>workshop-01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1096,6 +1053,24 @@
     </r>
   </si>
   <si>
+    <t>策展人導覽：王連晟、林晏竹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Curator-Led Tour: Lien-Cheng Wang, Yen-Ju Lin</t>
+  </si>
+  <si>
+    <t>Hydra is a browser-based live visual coding tool inspired by early analog video synthesizers. Using simple combinations of code, it allows users to generate a wide range of dynamic visual effects. This workshop introduces the fundamentals of Hydra, from basic shapes and animation to layering and modulation, guiding participants through its coding logic and exploring how a limited set of elements can be transformed into diverse visual compositions.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Riso printing involves separating a color image into individual layers, preparing each layer, and printing the colors one at a time. In this workshop, participants will use code to capture portraits, remove backgrounds, and separate the images into three-color halftone layers. By simulating halftone textures and randomized misregistration, the workshop explores how machines perceive and interpret people and images.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/01</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1104,17 +1079,100 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>六個假日，每日</t>
+      <t>（</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
       <t>15:00-15:30</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報名機制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術家講座I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術家講座II</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術家講座III</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術家講座IV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術家講座VI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術家講座V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist Talk I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist Talk II</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist Talk III</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist Talk IV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist Talk V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist Talk VI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動採預先線上報名，詳細報名資訊依官網及社群公告為主。活動前十分鐘，現場開放候補排隊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動導覽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1123,137 +1181,26 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>，現場報名</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>策展人導覽：王連晟、林晏竹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作人員導覽：傅智宏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作人員導覽：林宜蓁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Curator-Led Tour: Lien-Cheng Wang, Yen-Ju Lin</t>
-  </si>
-  <si>
-    <t>Staff-Led Tour: Chih-Hung Fu</t>
-  </si>
-  <si>
-    <t>Staff-Led Tour: Yi-Chen Lin</t>
-  </si>
-  <si>
-    <t>Hydra is a browser-based live visual coding tool inspired by early analog video synthesizers. Using simple combinations of code, it allows users to generate a wide range of dynamic visual effects. This workshop introduces the fundamentals of Hydra, from basic shapes and animation to layering and modulation, guiding participants through its coding logic and exploring how a limited set of elements can be transformed into diverse visual compositions.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Riso printing involves separating a color image into individual layers, preparing each layer, and printing the colors one at a time. In this workshop, participants will use code to capture portraits, remove backgrounds, and separate the images into three-color halftone layers. By simulating halftone textures and randomized misregistration, the workshop explores how machines perceive and interpret people and images.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/01</t>
+      <t>活動導覽請至服務台現場報名，並於導覽開始前</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15:00-15:30</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>報名機制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>人，預先報名</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>人，預先報名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>現場候補</t>
+      <t>分鐘至服務台集合。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1677,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>9</v>
@@ -1710,13 +1657,13 @@
         <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>82</v>
+        <v>61</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -1745,24 +1692,24 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>82</v>
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>20</v>
@@ -1776,22 +1723,22 @@
       <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>83</v>
+      <c r="J4" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>22</v>
@@ -1805,22 +1752,22 @@
       <c r="G5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>83</v>
+      <c r="J5" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>24</v>
@@ -1834,22 +1781,22 @@
       <c r="G6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>83</v>
+      <c r="J6" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
@@ -1863,22 +1810,22 @@
       <c r="G7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>83</v>
+      <c r="J7" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>31</v>
@@ -1892,22 +1839,22 @@
       <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>83</v>
+      <c r="J8" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>29</v>
@@ -1921,11 +1868,11 @@
       <c r="G9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>83</v>
+      <c r="J9" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -1999,7 +1946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2133D1F4-B331-41D0-9BD9-ECA306B553CF}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
@@ -2009,13 +1956,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="8"/>
@@ -2025,73 +1972,66 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>76</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>77</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C4" s="12"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>76</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>77</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>76</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C7" s="12"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>71</v>
+      <c r="A11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_活動清冊.xlsx
+++ b/assets/2026臺北數位藝術節_活動清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4320F78F-DE5F-4665-92C6-B33F3C82A4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A242200F-B0E1-410C-B4F7-A1341783C05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作坊&amp;講座" sheetId="7" r:id="rId1"/>
@@ -289,94 +289,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：郭紹蘭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dries Depoorter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Verena Friedrich</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、吳宜曄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>11/1</t>
     </r>
     <r>
@@ -404,127 +316,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：吳達坤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Stefan Tiefengraber</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Jed Berk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、林書瑜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術團體：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">C-LAB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>未來視覺實驗室</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>11/1</t>
     </r>
     <r>
@@ -552,42 +343,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：趙鐸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：沈宇軒、陳品蓁、鄭芳宜、郭子耘、謝佩庭</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>11/8</t>
     </r>
     <r>
@@ -615,42 +370,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：徐詩雨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：楊子毅、簡嘉誼、余柏霆、樊卓鏗、陳芷渝</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>11/8</t>
     </r>
     <r>
@@ -705,43 +424,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：蘇珀琪
-藝術家：陳政維、黃姿婷、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Bety Krňanská
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術團體：超級浪</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>11/15</t>
     </r>
     <r>
@@ -764,71 +446,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>15:30-16:40</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>與談人：邱誌勇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>藝術家：鄭先喻、何芯源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>藝術團體：無邊製造、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Assocreation</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -852,19 +469,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Panelist: Duo Chao
-Artist: Yu-Hsuan Shen, Pin-Jhen Chen, Fang-Yi Cheng, Tzu-Yung Kuo, Pei-Ting Hsieh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Panelist: Shih-Yu Hsu
 Artist: Tzu-I Yang, Chia-Yi Chien, Po-Ting Yu, Cheuk Hang Fan, Chih-Yu Chen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Chih-Yung Chiu
-Artist: Hsien-Yu Cheng, Hsin-Yuan Ho
-Artist Group: No Side Here, Assocreation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1201,6 +807,384 @@
         <charset val="136"/>
       </rPr>
       <t>分鐘至服務台集合。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：趙鐸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術家：沈宇軒、陳品蓁、鄭芳宜、謝佩庭</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Duo Chao
+Artist: Yu-Hsuan Shen, Pin-Jhen Chen, Fang-Yi Cheng, Pei-Ting Hsieh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：邱誌勇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術家：鄭先喻、何芯源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術團體：無邊製</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>造</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Chih-Yung Chiu
+Artist: Hsien-Yu Cheng, Hsin-Yuan Ho
+Artist Group: No Side Here</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：郭紹蘭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術家：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dries Depoorter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Verena Friedrich</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、吳宜曄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：吳達坤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術家：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stefan Tiefengraber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jed Berk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、林書瑜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術團體：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">C-LAB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>未來視覺實驗室</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：蘇珀琪
+藝術家：陳政維、黃姿婷、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bety Krňanská
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術團體：超級浪</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：徐詩雨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術家：楊子毅、簡嘉誼、余柏霆、樊卓鏗、陳芷渝</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1209,7 +1193,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1313,6 +1297,13 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1334,7 +1325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1363,6 +1354,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1624,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>9</v>
@@ -1639,13 +1636,13 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
@@ -1657,13 +1654,13 @@
         <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -1674,13 +1671,13 @@
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>18</v>
@@ -1692,187 +1689,187 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="54" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="81" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>35</v>
+      <c r="E5" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="54" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="54" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
+        <v>68</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -1956,13 +1953,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="8"/>
@@ -1972,57 +1969,57 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -2031,7 +2028,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_活動清冊.xlsx
+++ b/assets/2026臺北數位藝術節_活動清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A242200F-B0E1-410C-B4F7-A1341783C05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF96D40D-A0C0-4FA1-B48E-BF62782DC8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="97">
   <si>
     <t>簡介中文</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -450,11 +450,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Panelist: Jau-Lan Guo
-Artist: Dries Depoorter, Verena Friedrich, I-Yeh Wu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Artist: Tung-Yu Liu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -463,23 +458,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Panelist: Dar-Kuen Wu
-Artist: Stefan Tiefengraber, Jed Berk, Shu-Yu Lin
-Artist Group: C-LAB’s Future Vision Lab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Shih-Yu Hsu
-Artist: Tzu-I Yang, Chia-Yi Chien, Po-Ting Yu, Cheuk Hang Fan, Chih-Yu Chen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Po-Chi Su
-Artist: Cheng-Wei Chen, Tzu-Ting Huang, Bety Krňanská
-Artist Group: Hyper Wave</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>From Scratch: Hydra Live Coding Workshop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -548,6 +526,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>15:00-15:30</t>
@@ -573,6 +552,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>15:00-15:30</t>
@@ -653,6 +633,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>15:00-15:30</t>
@@ -712,6 +693,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>15:00-15:30</t>
@@ -794,6 +776,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>10</t>
@@ -921,15 +904,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>與談人：郭紹蘭</t>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Dar-Kuen Wu
+Artist: Stefan Tiefengraber, Jed Berk, Shu-Yu Lin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：吳達坤</t>
     </r>
     <r>
       <rPr>
@@ -960,7 +952,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Dries Depoorter</t>
+      <t>Stefan Tiefengraber</t>
     </r>
     <r>
       <rPr>
@@ -980,40 +972,129 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Verena Friedrich</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>、吳宜曄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>與談人：吳達坤</t>
+      <t>Jed Berk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、林書瑜</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：蘇珀琪
+藝術家：陳政維、黃姿婷、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bety Krňanská</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Po-Chi Su
+Artist: Cheng-Wei Chen, Tzu-Ting Huang, Bety Krňanská</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術團體：超級浪
+Artist Group: Hyper Wave
+尚未回覆先移除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術團體：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">C-LAB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>未來視覺實驗室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Artist Group: C-LAB’s Future Vision Lab
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>尚未回覆先移除</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>與談人中文介紹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>與談人英文介紹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：沈裕昌</t>
     </r>
     <r>
       <rPr>
@@ -1044,7 +1125,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Stefan Tiefengraber</t>
+      <t>Dries Depoorter</t>
     </r>
     <r>
       <rPr>
@@ -1064,17 +1145,45 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Jed Berk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>、林書瑜</t>
+      <t>Verena Friedrich</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、吳宜曄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Yu-Chang Shen
+Artist: Dries Depoorter, Verena Friedrich, I-Yeh Wu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：李佳霖</t>
     </r>
     <r>
       <rPr>
@@ -1095,97 +1204,142 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>藝術團體：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">C-LAB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>未來視覺實驗室</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>與談人：蘇珀琪
-藝術家：陳政維、黃姿婷、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Bety Krňanská
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>藝術團體：超級浪</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>與談人：徐詩雨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
       <t>藝術家：楊子毅、簡嘉誼、余柏霆、樊卓鏗、陳芷渝</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Lee-Chia Lin
+Artist: Tzu-I Yang, Chia-Yi Chien, Po-Ting Yu, Cheuk Hang Fan, Chih-Yu Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現任新北市美術館副館長,畢業於英國艾塞克斯大學(University of Essex)策展與藝術管理學系碩士。2003 至 2006 年間任職於台北當代藝術館展覽組研究助理,負責展覽策劃及統籌執行。其後於 2006 年至2010年間至北京工作，加入北京尤倫斯當代藝術中心以及北京中央美術學院美術館負責開館籌備及展覽規劃執行工作  。於 2010 年回臺後與藝術家林昆穎、陳志建、張耿豪以及張耿華共同成立藝術團體豪華朗機工,主要負責團隊發展及跨域計畫統籌製作。隨後於2014 至 2021年擔任鳳甲美術館館長,同時也是台北當代藝術中心的理事,除了年度展覽活動規劃及美術館營運發展之外,也積極推動國際交流事務。2022年中至 2024 年底於臺北市立美術館任副研究員,負責展覽及數位藝術計畫。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currently serving as Deputy Director of the New Taipei City Art Museum, she holds a master’s degree in Curating and Art Management from the University of Essex in the United Kingdom.
+From 2003 to 2006, she worked as a Research Assistant in the Exhibitions Department at the Museum of Contemporary Art Taipei (MOCA Taipei), where she was responsible for exhibition planning and coordination. Between 2006 and 2010, she worked in Beijing, contributing to the preparations for the opening of the Ullens Center for Contemporary Art (UCCA) and the CAFA Art Museum at the Central Academy of Fine Arts, as well as exhibition planning and implementation.
+After returning to Taiwan in 2010, she co-founded the art collective LuxuryLogico with artists Lin Kun-Ying, Chen Chih-Chien, Chang Keng-Hao, and Chang Keng-Hua. Her primary responsibilities included the collective’s development and the coordination and production of interdisciplinary projects.
+From 2014 to 2021, she served as Director of the Hong-gah Museum and as a board member of the Taipei Contemporary Art Center. In addition to overseeing annual exhibition programs and museum operations and development, she actively promoted international cultural exchange.
+From mid-2022 to the end of 2024, she served as an Associate Researcher at the Taipei Fine Arts Museum, focusing on exhibitions and digital art projects.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺大中國文學系碩士，現為北藝大美術系博士班學生，研究興趣為：佛教與宋明理學、影像與創傷、數位影像、操作影像等。經營粉專「藏書閣」，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Podcast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「洋紅色」。文章散見於「釀電影」、「放映週報」、「實驗波」、《藝術家雜誌》等。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He holds a master’s degree in Chinese Literature from National Taiwan University and is currently a doctoral student in the Department of Fine Arts at Taipei National University of the Arts.
+His research interests include Buddhism and Song–Ming Neo-Confucianism, images and trauma, digital imagery, and operational images.
+He runs the Facebook page Cang Shu Ge and the podcast Magenta. His writings have appeared in various publications and platforms, including Filmaholic, Funscreen Weekly, Experimental Wave, and Artist Magazine.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>現為國立清華大學藝術學院副院長、科技藝術研究所教授暨所長、藝術學院學士班主任，並榮獲清華—清鏡傑出人才講座、清華—台達傑出人才講座教授榮銜。同時為策展人、藝評家。學術專長為數位美學、科技文化研究、藝術評論與策展。曾獲第一屆與第二屆數位藝術評論入選獎、連續兩年獲得日本東京大學訪問學者資格（2020-2021），以及日本關西大學訪問學者資格（2023關西大學獎助）。曾策劃《靈魂的棲所：2024國際科技藝術展》（國美館）、《非日常路徑》（2023）、《鏡像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・映</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">像：80後的當代影像藝術展》（2022）、《虛幻生命：國際生物科技藝術展》（2021），《後數位人類紀：2019國際科技藝術展》（2019）、《2015-2016年台灣科技藝術節—潮》（2015-2016）、《奇幻視界—2014科技藝術展》（2014）、《第八屆臺北數位藝術節—超神經》、《第七屆臺北數位藝術節—第二自然》，著有《台灣數位表演與科技劇場》、《關鍵論述與在地實踐：在地化脈絡化下的新媒體藝術》，並編輯《藝術松》、《數位藝述》（共五輯）、《媒介擬想（4）：數位媒體與科技文化》、《媒體科技與文化全球化》等書。 </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He currently serves as Associate Dean of the College of Arts, Professor and Director of the Graduate Institute of Art and Technology, and Director of the Interdisciplinary Program of Arts at National Tsing Hua University (NTHU). He has also been awarded the honorary titles of NTHU–Ching Jing Distinguished Chair Professor and NTHU–Delta Distinguished Chair Professor. In addition to his academic roles, he is an active curator and art critic.
+His areas of expertise include digital aesthetics, technological culture studies, art criticism, and curatorial practice. He received recognition in both the first and second Digital Art Criticism Awards and was selected as a visiting scholar at the University of Tokyo for two consecutive years (2020–2021). In 2023, he was also awarded a visiting scholarship at Kansai University in Japan.
+His curatorial projects include Dwelling Place of the Soul: 2024 International Techno Art Exhibition (National Taiwan Museum of Fine Arts, 2024), Unordinary Paths (2023), Mirror Images: Contemporary Image Art of the Post-1980s Generation (2022), Illusory Life: International Bio Art Exhibition (2021), Post-Digital Anthropocene: 2019 International Techno Art Exhibition (2019), Tide: Taiwan Tech Art Festival 2015–2016, Fantastic Visions: 2014 Tech Art Exhibition, Super-Nerve: The 8th Taipei Digital Art Festival, and Second Nature: The 7th Taipei Digital Art Festival.
+He is the author of Digital Performance and Technological Theater in Taiwan and Critical Discourses and Local Practices: New Media Art in Localized Contexts. He has also edited several publications, including Art Pine, Digital Art Discourses (five volumes), Media Speculations (4): Digital Media and Technological Culture, and Media Technology and Cultural Globalization.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">沈裕昌，國立臺南藝術大學藝術創作理論研究所博士，現任國立臺北教育大學文化創意產業經營學系助理教授，專業領域為技術哲學與媒介研究、城市與空間文化研究、美學與當代藝術理論、當代策展與藝術實踐，發表〈宇宙技術論批判：與許煜商榷〉（韓國《美術史論壇》，2023）、〈人書之際，本末之辨：趙壹《非草書》論技藝與人的限度〉（《臺大文史哲學報》，2022）、〈書論的起源：崔瑗《草書勢》思想芻議〉（韓國《美術史論壇》，2019）等核心期刊論文，策劃「大肚之盟：山海間的物際外交」（臺中市立美術館，2026）、「辯者之石」（嘉義市立美術館，2026）等展覽。 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shen Yu-Chang holds a Ph.D. from the Doctoral Program in Art Creation and Theory at Tainan National University of the Arts. He is currently an Assistant Professor in the Department of Cultural and Creative Industries Management at National Taipei University of Education.
+His areas of expertise include the philosophy of technology and media studies, urban and spatial cultural studies, aesthetics and contemporary art theory, and contemporary curatorial practices and artistic production.
+His academic publications include “A Critique of Cosmotechnics: A Dialogue with Yuk Hui” (Art History Forum, South Korea, 2023), “Between Humans and Calligraphy: The Distinction Between Fundamentals and Peripherals—On Techniques and Human Limitations in Zhao Yi’s Fei Cao Shu” (Bulletin of the Department of Chinese Literature, National Taiwan University, 2022), and “The Origins of Calligraphic Theory: Reflections on Cui Yuan’s Cao Shu Shi” (Art History Forum, South Korea, 2019), among other articles published in leading academic journals.
+His curatorial projects include “The Dadu Alliance: Inter-Object Diplomacy Between Mountains and Sea” (Taichung Art Museum, 2026) and “The Philosopher’s Stone of Dialecticians” (Chiayi Art Museum, 2026).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">李佳霖畢業於台大外文系、中國美術學院當代藝術與社會思想研究所，研究與實踐關注方向為數位時代的文化研究、媒體理論與藝術創作。目前就讀台北藝術大學美術系博士班。曾任第十八屆臺北數位藝術節客座策展人。 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現任臺灣當代文化實驗場（C-LAB）當代藝術實驗平台暨總管理處總監。擁有豐富的創作、策展、教學、行政與寫作經驗，曾任臺北國際藝術村與寶藏巖國際藝術村總監、臺灣藝文空間連線（TASA）創會理事長、關渡美術館首席策展人。其創作與策展實踐長期關注當代藝術與新媒體藝術連結科技人文，以獨特的藝術語言反思全球化社會情境，探索「藝術無國界」的可能性。
+曾於多個國際機構駐村，包括2002年芬蘭NIFCA、2005年紐約Location One、2006年紐約ISCP、2008年東京Tokyo Wonder Site，以及2009年韓國釜山Open Space Bae。2004年獲亞洲文化協會（ACC）獎助與國巨科技藝術獎，作品為多所重要美術館與基金會收藏。
+自2008年起策劃多場重要展覽，包括《後民國－沒人共和國》（2011，高雄市立美術館，第10屆台新藝術獎評審團特別獎）、《AAA亞細亞安那其連線》（2014，東京Tokyo Wonder Site與台北關渡美術館）、《Roppongi Crossing 2016: My Body, Your Voice》（2016，東京森美術館）、《CHRONIQUES — 數位想像雙年展》（2020，法國馬賽）、第13屆光州雙年展臺灣館《雙迴聲》（2021，韓國光州）、《C-LAB未來媒體藝術節》（2021）、《創世熱 FeverGenesis》（2023，紐約Culture Lab LIC）、《未來媒體藝術節—奇異點》（2024，臺灣當代文化實驗場），以及《我們正成為 We Are Becoming》（2026，臺灣當代文化實驗場）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Li Chia-Lin graduated from the Department of Foreign Languages and Literatures at National Taiwan University and the Institute of Contemporary Art and Social Thought at the China Academy of Art.
+Her research and artistic practice focus on cultural studies in the digital age, media theory, and artistic creation. She is currently pursuing a Ph.D. in Fine Arts at Taipei National University of the Arts.
+She previously served as a Guest Curator for the 18th Taipei Digital Art Festival.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He currently serves as Director of the Contemporary Art Platform and General Administration Office at the Taiwan Contemporary Culture Lab (C-LAB). With extensive experience in artistic creation, curating, teaching, arts administration, and writing, he previously served as Director of Taipei Artist Village and Treasure Hill Artist Village, Founding Chairperson of the Taiwan Art Space Alliance (TASA), and Chief Curator of the Kuandu Museum of Fine Arts.
+His artistic and curatorial practices have long focused on the intersections of contemporary art, new media art, technology, and the humanities. Through his distinctive artistic language, he reflects on the conditions of a globalized society and explores the possibilities of art beyond borders.
+He has participated in international artist residency programs at NIFCA in Finland (2002), Location One in New York (2005), the International Studio &amp; Curatorial Program (ISCP) in New York (2006), Tokyo Wonder Site in Japan (2008), and Open Space Bae in Busan, South Korea (2009). In 2004, he received a fellowship from the Asian Cultural Council (ACC) and the Yageo Tech-Art Award. His works are held in the collections of major museums and foundations.
+Since 2008, he has curated numerous major exhibitions, including “Post-Republic: The Republic of No One” (Kaohsiung Museum of Fine Arts, 2011), which received the Jury's Special Award at the 10th Taishin Arts Awards; “AAA: Asia Anarchy Alliance” (Tokyo Wonder Site and Kuandu Museum of Fine Arts, 2014); “Roppongi Crossing 2016: My Body, Your Voice” (Mori Art Museum, Tokyo, 2016); “CHRONIQUES — Biennale of Digital Imaginaries” (Marseille, France, 2020); “Double Echoing,” the Taiwan Pavilion at the 13th Gwangju Biennale (Gwangju, South Korea, 2021); “C-LAB Future Media Arts Festival” (2021); “FeverGenesis” (Culture Lab LIC, New York, 2023); “Future Media Arts Festival: Singularity” (Taiwan Contemporary Culture Lab, 2024); and “We Are Becoming” (Taiwan Contemporary Culture Lab, 2026).</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1193,7 +1347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1304,6 +1458,20 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1325,7 +1493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1360,6 +1528,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1576,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1584,15 +1764,17 @@
     <col min="3" max="3" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="2" customWidth="1"/>
-    <col min="8" max="10" width="21.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="45.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="21.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="2" customWidth="1"/>
+    <col min="10" max="12" width="21.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="45.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -1608,27 +1790,35 @@
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="N1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1636,34 +1826,34 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1671,268 +1861,472 @@
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="54" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="54" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="C5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="F6" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="54" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="54" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="8" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="C9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F9" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="81" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="L9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="51" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="54" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="54" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F10" s="18"/>
+      <c r="G10" s="16"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F11" s="18"/>
+      <c r="G11" s="16"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+    </row>
+    <row r="14" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F14" s="18"/>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
-      <c r="B15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
-      <c r="B16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
-      <c r="B17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
-      <c r="B18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
-      <c r="B19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
-      <c r="B20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
-      <c r="B21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1953,13 +2347,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="8"/>
@@ -1969,57 +2363,57 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -2028,7 +2422,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_活動清冊.xlsx
+++ b/assets/2026臺北數位藝術節_活動清冊.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="104">
   <si>
     <t>簡介中文</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1341,6 +1341,27 @@
 He has participated in international artist residency programs at NIFCA in Finland (2002), Location One in New York (2005), the International Studio &amp; Curatorial Program (ISCP) in New York (2006), Tokyo Wonder Site in Japan (2008), and Open Space Bae in Busan, South Korea (2009). In 2004, he received a fellowship from the Asian Cultural Council (ACC) and the Yageo Tech-Art Award. His works are held in the collections of major museums and foundations.
 Since 2008, he has curated numerous major exhibitions, including “Post-Republic: The Republic of No One” (Kaohsiung Museum of Fine Arts, 2011), which received the Jury's Special Award at the 10th Taishin Arts Awards; “AAA: Asia Anarchy Alliance” (Tokyo Wonder Site and Kuandu Museum of Fine Arts, 2014); “Roppongi Crossing 2016: My Body, Your Voice” (Mori Art Museum, Tokyo, 2016); “CHRONIQUES — Biennale of Digital Imaginaries” (Marseille, France, 2020); “Double Echoing,” the Taiwan Pavilion at the 13th Gwangju Biennale (Gwangju, South Korea, 2021); “C-LAB Future Media Arts Festival” (2021); “FeverGenesis” (Culture Lab LIC, New York, 2023); “Future Media Arts Festival: Singularity” (Taiwan Contemporary Culture Lab, 2024); and “We Are Becoming” (Taiwan Contemporary Culture Lab, 2026).</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>採線上預先報名，詳細報名資訊請參閱報名連結。活動開始前 10 分鐘開放現場候補排隊。</t>
+  </si>
+  <si>
+    <t>10/31（六）15:00-16:00</t>
+  </si>
+  <si>
+    <t>11/01（日）15:00-16:00</t>
+  </si>
+  <si>
+    <t>11/07（六）15:00-16:00</t>
+  </si>
+  <si>
+    <t>11/08（日）15:00-16:00</t>
+  </si>
+  <si>
+    <t>11/14（六）15:00-16:00</t>
+  </si>
+  <si>
+    <t>11/15（日）15:00-16:00</t>
   </si>
 </sst>
 </file>
@@ -1755,9 +1776,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
   <dimension ref="A1:N58"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.28515625" style="2" customWidth="1"/>
@@ -1774,7 +1795,7 @@
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -1818,7 +1839,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1847,13 +1868,13 @@
         <v>49</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1890,7 +1911,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="54" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="54" ns3:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>30</v>
       </c>
@@ -1925,7 +1946,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="54" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="54" ns3:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>30</v>
       </c>
@@ -1963,7 +1984,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="51" ns3:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
@@ -1998,7 +2019,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="54" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="54" ns3:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
@@ -2033,7 +2054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="51" ns3:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
@@ -2068,7 +2089,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="42.75" ns3:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>30</v>
       </c>
@@ -2106,7 +2127,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="D10" s="4"/>
@@ -2114,7 +2135,7 @@
       <c r="G10" s="16"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="D11" s="4"/>
@@ -2122,51 +2143,51 @@
       <c r="G11" s="16"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ns3:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ns3:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
     </row>
-    <row r="14" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="D14" s="4"/>
       <c r="F14" s="18"/>
       <c r="G14" s="16"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ns3:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ns3:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ns3:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ns3:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ns3:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
@@ -2174,178 +2195,178 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="13.5" ns3:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ns3:dyDescent="0.2">
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ns3:dyDescent="0.2">
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ns3:dyDescent="0.2">
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ns3:dyDescent="0.2">
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ns3:dyDescent="0.2">
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ns3:dyDescent="0.2">
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ns3:dyDescent="0.2">
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ns3:dyDescent="0.2">
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ns3:dyDescent="0.2">
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ns3:dyDescent="0.2">
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ns3:dyDescent="0.2">
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
     </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:7" ns3:dyDescent="0.2">
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
     </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="6:7" ns3:dyDescent="0.2">
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
     </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="6:7" ns3:dyDescent="0.2">
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
     </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="6:7" ns3:dyDescent="0.2">
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
     </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="6:7" ns3:dyDescent="0.2">
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
     </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:7" ns3:dyDescent="0.2">
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
     </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:7" ns3:dyDescent="0.2">
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
     </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="6:7" ns3:dyDescent="0.2">
       <c r="F40" s="16"/>
       <c r="G40" s="16"/>
     </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="6:7" ns3:dyDescent="0.2">
       <c r="F41" s="16"/>
       <c r="G41" s="16"/>
     </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="6:7" ns3:dyDescent="0.2">
       <c r="F42" s="16"/>
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="6:7" ns3:dyDescent="0.2">
       <c r="F43" s="16"/>
       <c r="G43" s="16"/>
     </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="6:7" ns3:dyDescent="0.2">
       <c r="F44" s="16"/>
       <c r="G44" s="16"/>
     </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="6:7" ns3:dyDescent="0.2">
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
     </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="6:7" ns3:dyDescent="0.2">
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
     </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="6:7" ns3:dyDescent="0.2">
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
     </row>
-    <row r="48" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="6:7" ns3:dyDescent="0.2">
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="6:7" ns3:dyDescent="0.2">
       <c r="F49" s="16"/>
       <c r="G49" s="16"/>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="6:7" ns3:dyDescent="0.2">
       <c r="F50" s="16"/>
       <c r="G50" s="16"/>
     </row>
-    <row r="51" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="6:7" ns3:dyDescent="0.2">
       <c r="F51" s="16"/>
       <c r="G51" s="16"/>
     </row>
-    <row r="52" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="6:7" ns3:dyDescent="0.2">
       <c r="F52" s="16"/>
       <c r="G52" s="16"/>
     </row>
-    <row r="53" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="6:7" ns3:dyDescent="0.2">
       <c r="F53" s="16"/>
       <c r="G53" s="16"/>
     </row>
-    <row r="54" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="6:7" ns3:dyDescent="0.2">
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
     </row>
-    <row r="55" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="6:7" ns3:dyDescent="0.2">
       <c r="F55" s="16"/>
       <c r="G55" s="16"/>
     </row>
-    <row r="56" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="6:7" ns3:dyDescent="0.2">
       <c r="F56" s="16"/>
       <c r="G56" s="16"/>
     </row>
-    <row r="57" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="6:7" ns3:dyDescent="0.2">
       <c r="F57" s="16"/>
       <c r="G57" s="16"/>
     </row>
-    <row r="58" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="6:7" ns3:dyDescent="0.2">
       <c r="F58" s="16"/>
       <c r="G58" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2133D1F4-B331-41D0-9BD9-ECA306B553CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2133D1F4-B331-41D0-9BD9-ECA306B553CF}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ns3:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>39</v>
       </c>
@@ -2361,9 +2382,9 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ns3:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>47</v>
@@ -2372,55 +2393,55 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" ns3:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="12"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ns3:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="12"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ns3:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="12"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ns3:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="12"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ns3:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="12"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ns3:dyDescent="0.25">
       <c r="A11" s="10"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ns3:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>67</v>
       </c>
@@ -2428,6 +2449,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>